--- a/delivery_routes_1_8_{}.xlsx
+++ b/delivery_routes_1_8_{}.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Group 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Group 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Group 3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,37 +438,37 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>כתובת</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>שם</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>כתובת</t>
+          <t>Unnamed: 1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>מיקום</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>תמונה</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>packages</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>פלאפון</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -476,35 +478,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>להביא לו החודש</t>
+          <t>השבוע מחלקים?</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>סה"כ מנות החודש</t>
+          <t>כמה מארזים</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>מי מחלק?</t>
+          <t>Unnamed: 10</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> אריאל</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>longitude</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
@@ -516,27 +513,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>כלילת יופי 2/8 אריאל</t>
+          <t>כלילת יופי 2/8 אריאל + אריאל</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">מור שמואל </t>
+          <t>מור שמואל</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>כלילת יופי 2/8</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>050-630-2010⁩</t>
+          <t>050-630-2010</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -546,17 +545,18 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>32.0992363</v>
+      </c>
       <c r="N2" t="n">
-        <v>32.0992363</v>
+        <v>35.2050327</v>
       </c>
       <c r="O2" t="n">
-        <v>35.2050327</v>
-      </c>
-      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -566,27 +566,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>הגלבוע 11/א דירה 6 אריאל</t>
+          <t>הגלבוע 11 א, דירה 6 אריאל + אריאל</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ענבל דגא</t>
+          <t>עינבל דגא</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>הגלבוע 11/א דירה 6</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>הגלבוע 11 א, דירה 6</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 054-260-3993</t>
+          <t>054-260-3993</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -596,17 +598,18 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>32.104501</v>
+      </c>
       <c r="N3" t="n">
-        <v>32.104501</v>
+        <v>35.2019794</v>
       </c>
       <c r="O3" t="n">
-        <v>35.2019794</v>
-      </c>
-      <c r="P3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -616,27 +619,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>שער הגיא 11/4 אריאל</t>
+          <t>שער הגיא 12/7 אריאל + אריאל</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>אלה</t>
+          <t>דקלה כהן</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>שער הגיא 11/4</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>שער הגיא 12/7</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>053-250-5858⁩</t>
+          <t>050-260-7706⁩</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -646,17 +651,18 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32.1037865</v>
+      </c>
       <c r="N4" t="n">
-        <v>32.1033567</v>
+        <v>35.1984874</v>
       </c>
       <c r="O4" t="n">
-        <v>35.1990039</v>
-      </c>
-      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -666,27 +672,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>דרך הציונות 69/2 אריאל</t>
+          <t>דרך עפרון 3 דירה 6 אריאל + אריאל</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>דליה חיון</t>
+          <t>מיכאל</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>דרך הציונות 69/2</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>דרך עפרון 3 דירה 6</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>052-442-5993⁩</t>
+          <t>054-725-6444⁩</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -696,17 +704,18 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>32.1042825</v>
+      </c>
       <c r="N5" t="n">
-        <v>32.1053517</v>
+        <v>35.1737117</v>
       </c>
       <c r="O5" t="n">
-        <v>35.1953157</v>
-      </c>
-      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -716,31 +725,33 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>דרך הציונות 2/10 אריאל</t>
+          <t>אשקובית דרך עפרון 43 אריאל + אריאל</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>מורן נוגה</t>
+          <t>מיטל בכר</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>דרך הציונות 2/10</t>
+          <t xml:space="preserve"> אריאל</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>הכניסה מרחוב אבנר, קומה 3 דלת שמאל</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
+          <t>אשקובית דרך עפרון 43</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=32.1041561,35.1734082&amp;z=17&amp;hl=he</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>054-884-2203⁩</t>
+          <t>054-811-3765</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -750,17 +761,18 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="M6" t="n">
+        <v>32.1038591</v>
+      </c>
       <c r="N6" t="n">
-        <v>32.1074157</v>
+        <v>35.1720058</v>
       </c>
       <c r="O6" t="n">
-        <v>35.181759</v>
-      </c>
-      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -770,47 +782,54 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>הפסגה 4/3 אריאל</t>
+          <t>הורדים 4/6 אריאל + אריאל</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>אליהו</t>
+          <t>מיכאלה הלוי</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>הפסגה 4/3</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>הורדים 4/6</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>053-342-3530</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>050-878-6400</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>*בבקשה שלא ילכו אליה תושבים שגדלו ביקיר*</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>כן</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>32.1021247</v>
+      </c>
       <c r="N7" t="n">
-        <v>32.1067516</v>
+        <v>35.1713272</v>
       </c>
       <c r="O7" t="n">
-        <v>35.1766665</v>
-      </c>
-      <c r="P7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -820,27 +839,499 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>שיקמה 6 אריאל</t>
+          <t>השקמה 6 כניסה 4 אריאל + אריאל</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>צופית ראובני</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>השקמה 6 כניסה 4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>052-852-3123</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>נא להתקשר לפני ולוודא שאין לה אורחים בבית</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>31.9512433</v>
+      </c>
+      <c r="N8" t="n">
+        <v>34.9315856</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Route Order</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>כתובת</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>שם</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>מיקום</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>תמונה</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>פלאפון</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>הערות</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>השבוע מחלקים?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>כמה מארזים</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>רמת הגולן 6 קומה 4 דירה 26 אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>גניה שבצקי</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>רמת הגולן 6 קומה 4 דירה 26</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>כניסה E</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>054-424-0508⁩</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>32.1050621</v>
+      </c>
+      <c r="N2" t="n">
+        <v>35.198584</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>דרך הציונות 69/2 אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>דליה חיון</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>דרך הציונות 69/2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>052-442-5993</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>32.1053517</v>
+      </c>
+      <c r="N3" t="n">
+        <v>35.1953157</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>הערבה 63/1 אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>תיקי זיתוני</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>הערבה 63/1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>54-538-0358</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32.1046435</v>
+      </c>
+      <c r="N4" t="n">
+        <v>35.1818844</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>צהל 1 דירה 10 אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>מיטל אביב</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>צהל 1 דירה 10</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>32.1064655</v>
+      </c>
+      <c r="N5" t="n">
+        <v>35.1819463</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>אורי בר און 19/10 אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>דוד</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>אורי בר און 19/10</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0533010381</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>32.1061292</v>
+      </c>
+      <c r="N6" t="n">
+        <v>35.1812882</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>אורי בראון 32/1 אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>קטיה</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>אורי בראון 32/1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/32%C2%B006'17.4%22N+35%C2%B010'39.2%22E/@32.1048367,35.1797539,17z/data=!3m1!4b1!4m4!3m3!8m2!3d32.1048367!4d35.1775652?hl=he&amp;entry=ttu</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0506590513</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>32.105043</v>
+      </c>
+      <c r="N7" t="n">
+        <v>35.17897019999999</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>השקמה 6 אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>מאיה טוויל</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>שיקמה 6</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>השקמה 6</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>050-4203805</t>
+          <t>050-420-3805</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -850,162 +1341,448 @@
         </is>
       </c>
       <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>32.1046376</v>
+      </c>
+      <c r="N8" t="n">
+        <v>35.1745145</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Route Order</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>כתובת</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>שם</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>מיקום</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>תמונה</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>פלאפון</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>הערות</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>השבוע מחלקים?</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>כמה מארזים</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 10</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>latitude</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>longitude</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>הפסגה 4/3 אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>אליהו</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>הפסגה 4/3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>053-342-3530</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>32.1067516</v>
+      </c>
+      <c r="N2" t="n">
+        <v>35.1766665</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>דרך הציונות 2/10 אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>קובי נוגה</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>דרך הציונות 2/10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0532465004</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>32.1074157</v>
+      </c>
+      <c r="N3" t="n">
+        <v>35.181759</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>דרך הציונות 2 דירה 10 קומה עליונה אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>מורן נוגה</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>דרך הציונות 2 דירה 10 קומה עליונה</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps?q=32.1069916,35.1820029&amp;z=17&amp;hl=he</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>054-884-2203</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>נוגה מורן לעדכן שהכניסה היא מרחוב אבנר. קומה 3 דלת שמאל</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32.1074157</v>
+      </c>
+      <c r="N4" t="n">
+        <v>35.181759</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>32.1046376</v>
-      </c>
-      <c r="O8" t="n">
-        <v>35.1745145</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>אשקובית דרך עפרון 43 אריאל</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>מיטל בכר</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>אשקובית דרך עפרון 43</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>548113765</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>32.1038591</v>
-      </c>
-      <c r="O9" t="n">
-        <v>35.1720058</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>הורדים 4/14 אריאל</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>יעל</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>הורדים 4/14</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>050-949-4047⁩</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>כן</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>32.1021247</v>
-      </c>
-      <c r="O10" t="n">
-        <v>35.1713272</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>השקמה 6/4 אריאל</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>צופית ראובני</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>השקמה 6/4</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>052-852-3123⁩</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>31.7848643</v>
-      </c>
-      <c r="O11" t="n">
-        <v>35.2116785</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>הנחשונים 7/5 אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>בלה תמיר</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>הנחשונים 7/5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>052-378-8974</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>32.1072925</v>
+      </c>
+      <c r="N5" t="n">
+        <v>35.1798051</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>דרך הנחשונים 28 אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>אנסטסיה</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>דרך הנחשונים 28</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>055-8838618</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ד</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>ד</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>32.1078723</v>
+      </c>
+      <c r="N6" t="n">
+        <v>35.1779164</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>רחוב כלניות 1 דירה 6 אריאל + אריאל</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>רוזי עבודי</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> אריאל</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>רחוב כלניות 1 דירה 6</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/32%C2%B006'08.9%22N+35%C2%B010'21.2%22E/@32.1024613,35.174732,17z/data=!3m1!4b1!4m4!3m3!8m2!3d32.1024613!4d35.1725433?hl=he&amp;entry=ttu</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>054-942-6970</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">קומה אחרונה. </t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>32.818463</v>
+      </c>
+      <c r="N7" t="n">
+        <v>35.088241</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
